--- a/outputs/evaluation/architecture/validation/CF_M04/run_1/CF_M04_arch_eval_llm_report.xlsx
+++ b/outputs/evaluation/architecture/validation/CF_M04/run_1/CF_M04_arch_eval_llm_report.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L6"/>
+  <dimension ref="A1:L5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -481,7 +481,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>AU_12</t>
+          <t>AU_10</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -496,17 +496,17 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>External service for artificial intelligence suggestions.</t>
+          <t>External service used for generating intelligent response suggestions for reviews.</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>55, 68</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>AU_08</t>
+          <t>AU_02</t>
         </is>
       </c>
       <c r="G2" t="inlineStr"/>
@@ -529,7 +529,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>AU_19</t>
+          <t>AU_18</t>
         </is>
       </c>
       <c r="B3" t="inlineStr"/>
@@ -540,42 +540,42 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Firebase, used for complementary functionalities like notifications.</t>
+          <t>The frontend is the mobile application developed with Flutter that acts as the presentation layer [...] and of performing the necessary requests to the back-end to obtain or modify information.</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>54</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>AU_02, AU_15</t>
+          <t>AU_01, AU_02</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>backend, firebase</t>
+          <t>frontend, backend</t>
         </is>
       </c>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr">
         <is>
-          <t>CF_M04_AU27</t>
+          <t>CF_M04_AU01</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Firebase</t>
+          <t>Frontend</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>Firebase for complementary functionalities (notifications, services associated).</t>
+          <t>From the user's point of view, interaction with the system is carried out through a mobile application developed with Flutter, which acts as a presentation layer (front-end)</t>
         </is>
       </c>
       <c r="L3" t="n">
-        <v>0.8454</v>
+        <v>0.7971</v>
       </c>
     </row>
     <row r="4">
@@ -596,17 +596,17 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Data is exchanged in JSON format, using standard HTTP methods like GET and POST.</t>
+          <t>The communication between the front-end and the back-end is carried out through a REST API, using JSON format messages for both requests and responses.</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>55</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>AU_16</t>
+          <t>AU_19</t>
         </is>
       </c>
       <c r="G4" t="inlineStr"/>
@@ -644,7 +644,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>The system architecture is based on a mobile application (frontend) that makes requests to a backend server.</t>
+          <t>The system follows a client-server architecture where the mobile application (frontend) makes requests to a server (backend) that processes them.</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -672,58 +672,6 @@
       </c>
       <c r="L5" t="n">
         <v>0.727</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>P_06</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Dependency Inversion</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Design Pattern</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>The domain defines interfaces that are implemented by the infrastructure.</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>66</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>P_02</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>CF_M04_AU20</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>User</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>Users: Application customers who use the new features and provide feedback.</t>
-        </is>
-      </c>
-      <c r="L6" t="n">
-        <v>0.6701</v>
       </c>
     </row>
   </sheetData>
